--- a/tame_output/ON/bt/strategyON_20240130.xlsx
+++ b/tame_output/ON/bt/strategyON_20240130.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>52.7%</t>
+          <t>53.5%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,16 +610,16 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.2%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1854</v>
+        <v>1855</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,7 +628,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-01-28</t>
+          <t>2024-01-29</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>18.3%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>3.6%</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1854</v>
+        <v>1855</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-01-28</t>
+          <t>2024-01-29</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>64.4%</t>
+          <t>64.3%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>2.0%</t>
+          <t>2.1%</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>31.0%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -926,7 +926,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1854</v>
+        <v>1855</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-01-28</t>
+          <t>2024-01-29</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>1.7%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>100.7%</t>
+          <t>100.6%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1089,11 +1089,11 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>58.6%</t>
+          <t>58.5%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1854</v>
+        <v>1855</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-01-28</t>
+          <t>2024-01-29</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>96.0%</t>
+          <t>95.9%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>40.4%</t>
+          <t>40.3%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>2.8%</t>
         </is>
       </c>
     </row>
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1854</v>
+        <v>1855</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-01-28</t>
+          <t>2024-01-29</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-155.8%</t>
+          <t>-155.7%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1854</v>
+        <v>1855</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-01-28</t>
+          <t>2024-01-29</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>123.5%</t>
+          <t>123.4%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>2.9%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1857"/>
+  <dimension ref="A1:G1858"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44256,7 +44256,7 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287799389351032</v>
+        <v>3.28737757613002</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
@@ -44272,6 +44272,29 @@
       </c>
       <c r="G1857" t="n">
         <v>4.487947771474467</v>
+      </c>
+    </row>
+    <row r="1858">
+      <c r="A1858" s="2" t="n">
+        <v>45320</v>
+      </c>
+      <c r="B1858" t="n">
+        <v>3.316633580677844</v>
+      </c>
+      <c r="C1858" t="n">
+        <v>3.137738646563379</v>
+      </c>
+      <c r="D1858" t="n">
+        <v>1.632562930543114</v>
+      </c>
+      <c r="E1858" t="n">
+        <v>3.790407394466878</v>
+      </c>
+      <c r="F1858" t="n">
+        <v>2.253303419352245</v>
+      </c>
+      <c r="G1858" t="n">
+        <v>4.489720698174726</v>
       </c>
     </row>
   </sheetData>
